--- a/project-a/tables/excel/MonsterTable.xlsx
+++ b/project-a/tables/excel/MonsterTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="monster_intents" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="monsters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_intents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monsters" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_template</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>공격력의 100% 피해.</t>
+          <t>공격력의 {0}% 피해.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>공격력의 150% 피해.</t>
+          <t>공격력의 {0}% 피해.</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>실드 80 획득.</t>
+          <t>실드 {0} 획득.</t>
         </is>
       </c>
     </row>

--- a/project-a/tables/excel/MonsterTable.xlsx
+++ b/project-a/tables/excel/MonsterTable.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Stab</t>
+          <t>찌르기</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Heavy Blow</t>
+          <t>강타</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brace</t>
+          <t>방어</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mire Imp</t>
+          <t>마이어 임프</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bog Stalker</t>
+          <t>늪 추적자</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -757,7 +757,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bone Crawler</t>
+          <t>뼈 크롤러</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -777,7 +777,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gravebound Crawler</t>
+          <t>무덤 크롤러</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frost Revenant</t>
+          <t>프로스트 레버넌트</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -817,7 +817,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Crown Acolyte</t>
+          <t>왕관 시종</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Abyssal Crown Guardian</t>
+          <t>심연 왕관 수호자</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/project-a/tables/excel/MonsterTable.xlsx
+++ b/project-a/tables/excel/MonsterTable.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_intents" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monsters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterIntents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monsters" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A2:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -425,7 +425,6 @@
     <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
@@ -434,32 +433,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>display_name</t>
+          <t>DisplayName</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>intent_type</t>
+          <t>IntentType</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>icon_label</t>
+          <t>IconLabel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>description_template</t>
+          <t>DescriptionTemplate</t>
         </is>
       </c>
     </row>
@@ -530,7 +529,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>stab</t>
+          <t>Stab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -540,7 +539,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -560,7 +559,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>heavy_blow</t>
+          <t>HeavyBlow</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -570,7 +569,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -590,7 +589,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>brace</t>
+          <t>Brace</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -600,7 +599,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>block</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -628,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A2:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -637,7 +636,6 @@
     <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
@@ -646,22 +644,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>display_name</t>
+          <t>DisplayName</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>action_count</t>
+          <t>ActionCount</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>intents[]</t>
+          <t>Intents[]</t>
         </is>
       </c>
     </row>
@@ -712,7 +710,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>mire_imp</t>
+          <t>MireImp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -725,14 +723,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stab,brace,heavy_blow</t>
+          <t>Stab,Brace,HeavyBlow</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>bog_stalker</t>
+          <t>BogStalker</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -745,14 +743,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stab,stab,heavy_blow</t>
+          <t>Stab,Stab,HeavyBlow</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>bone_crawler</t>
+          <t>BoneCrawler</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -765,14 +763,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>heavy_blow,stab,brace</t>
+          <t>HeavyBlow,Stab,Brace</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>gravebound_crawler</t>
+          <t>GraveboundCrawler</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -785,14 +783,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>brace,stab,heavy_blow</t>
+          <t>Brace,Stab,HeavyBlow</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>frost_revenant</t>
+          <t>FrostRevenant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -805,14 +803,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>brace,heavy_blow,stab,heavy_blow</t>
+          <t>Brace,HeavyBlow,Stab,HeavyBlow</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>crown_acolyte</t>
+          <t>CrownAcolyte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -825,14 +823,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>heavy_blow,brace,heavy_blow</t>
+          <t>HeavyBlow,Brace,HeavyBlow</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>abyssal_crown_guardian</t>
+          <t>AbyssalCrownGuardian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -845,7 +843,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>heavy_blow,brace,heavy_blow,stab</t>
+          <t>HeavyBlow,Brace,HeavyBlow,Stab</t>
         </is>
       </c>
     </row>
